--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43086420318268</v>
+        <v>2.345015433017185</v>
       </c>
       <c r="D2" t="n">
-        <v>14.56896391946234</v>
+        <v>2.367456636912631</v>
       </c>
       <c r="E2" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F2" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.21540865731141</v>
+        <v>1.660003906813104</v>
       </c>
       <c r="D3" t="n">
-        <v>9.973095199349233</v>
+        <v>1.620627969894251</v>
       </c>
       <c r="E3" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F3" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.68972934087709</v>
+        <v>2.549581017892527</v>
       </c>
       <c r="D4" t="n">
-        <v>15.8908484312697</v>
+        <v>2.582262870081326</v>
       </c>
       <c r="E4" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F4" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.05862684846219</v>
+        <v>1.634526862875106</v>
       </c>
       <c r="D5" t="n">
-        <v>10.01079090775924</v>
+        <v>1.626753522510876</v>
       </c>
       <c r="E5" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F5" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.52964716715852</v>
+        <v>4.473567664663259</v>
       </c>
       <c r="D6" t="n">
-        <v>27.53981010545787</v>
+        <v>4.475219142136904</v>
       </c>
       <c r="E6" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F6" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.76748745988234</v>
+        <v>4.674716712230881</v>
       </c>
       <c r="D7" t="n">
-        <v>28.69866398864123</v>
+        <v>4.663532898154199</v>
       </c>
       <c r="E7" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F7" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.48333891210848</v>
+        <v>4.466042573217628</v>
       </c>
       <c r="D8" t="n">
-        <v>27.617670734406</v>
+        <v>4.487871494340975</v>
       </c>
       <c r="E8" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F8" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.85057093562006</v>
+        <v>2.73821777703826</v>
       </c>
       <c r="D9" t="n">
-        <v>16.86565022074261</v>
+        <v>2.740668160870674</v>
       </c>
       <c r="E9" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F9" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.30488812603905</v>
+        <v>1.999544320481346</v>
       </c>
       <c r="D10" t="n">
-        <v>12.11338913848958</v>
+        <v>1.968425735004558</v>
       </c>
       <c r="E10" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F10" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.63278551343032</v>
+        <v>4.002827645932427</v>
       </c>
       <c r="D11" t="n">
-        <v>24.42764662718007</v>
+        <v>3.969492576916761</v>
       </c>
       <c r="E11" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F11" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.64401302773717</v>
+        <v>4.167152117007291</v>
       </c>
       <c r="D12" t="n">
-        <v>25.48743438573173</v>
+        <v>4.141708087681407</v>
       </c>
       <c r="E12" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F12" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.46902327902191</v>
+        <v>4.30121628284106</v>
       </c>
       <c r="D13" t="n">
-        <v>26.52367385866523</v>
+        <v>4.310097002033101</v>
       </c>
       <c r="E13" t="n">
-        <v>7.059430037729</v>
+        <v>1.147157381130963</v>
       </c>
       <c r="F13" t="n">
-        <v>7.080132081532197</v>
+        <v>1.150521463248982</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
